--- a/data/trans_orig/P36BPD10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36994</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47328</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>104536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144761</t>
+          <t>147731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93388</t>
+          <t>94232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122595</t>
+          <t>121739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206114</t>
+          <t>207734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256263</t>
+          <t>261250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199952</t>
+          <t>198838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150744</t>
+          <t>150694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179441</t>
+          <t>180260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>319373</t>
+          <t>314750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>371987</t>
+          <t>367219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81929</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127972</t>
+          <t>128280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>79990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112642</t>
+          <t>112763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167973</t>
+          <t>169574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228361</t>
+          <t>229548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236348</t>
+          <t>233125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>292932</t>
+          <t>292134</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252609</t>
+          <t>253630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>294108</t>
+          <t>295092</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>503707</t>
+          <t>503063</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>572276</t>
+          <t>578657</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125408</t>
+          <t>125977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178643</t>
+          <t>179910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127064</t>
+          <t>128390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163970</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262162</t>
+          <t>260811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>330188</t>
+          <t>329475</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36819</t>
+          <t>34464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45669</t>
+          <t>45538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73099</t>
+          <t>74730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117280</t>
+          <t>116666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152865</t>
+          <t>151466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105135</t>
+          <t>104976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>133554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229378</t>
+          <t>231251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275580</t>
+          <t>276838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>138275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171516</t>
+          <t>172632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178920</t>
+          <t>181880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212469</t>
+          <t>211802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329599</t>
+          <t>327119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375913</t>
+          <t>376487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62896</t>
+          <t>62649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74185</t>
+          <t>72584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111342</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109667</t>
+          <t>108583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289740</t>
+          <t>280651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197767</t>
+          <t>197688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386349</t>
+          <t>393860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176589</t>
+          <t>175079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>216013</t>
+          <t>216667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168962</t>
+          <t>175959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337580</t>
+          <t>339613</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>367967</t>
+          <t>358198</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>542157</t>
+          <t>540495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43178</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>66159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>57889</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88699</t>
+          <t>88703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117188</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107477</t>
+          <t>107977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130029</t>
+          <t>130414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148675</t>
+          <t>147979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165936</t>
+          <t>166024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262489</t>
+          <t>262445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291097</t>
+          <t>290936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>41541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104049</t>
+          <t>103001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133424</t>
+          <t>133430</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102328</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127921</t>
+          <t>128331</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213622</t>
+          <t>213010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251190</t>
+          <t>251168</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136752</t>
+          <t>136509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112639</t>
+          <t>111824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138399</t>
+          <t>138525</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228857</t>
+          <t>227909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267336</t>
+          <t>267907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67655</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>121817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79311</t>
+          <t>78975</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92942</t>
+          <t>90453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>184813</t>
+          <t>185156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>183648</t>
+          <t>181266</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>238977</t>
+          <t>236563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107716</t>
+          <t>107020</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301774</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271630</t>
+          <t>264998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>516633</t>
+          <t>515674</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>288688</t>
+          <t>291153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>350317</t>
+          <t>352215</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>473220</t>
+          <t>476202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>713420</t>
+          <t>715263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>786844</t>
+          <t>789957</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1095385</t>
+          <t>1114346</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65762</t>
+          <t>65783</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>39277</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>63026</t>
+          <t>62569</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60173</t>
+          <t>51637</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118036</t>
+          <t>118254</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>660306</t>
+          <t>659651</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>839676</t>
+          <t>836288</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>504092</t>
+          <t>505953</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>548791</t>
+          <t>548994</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1191099</t>
+          <t>1187447</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1409822</t>
+          <t>1409849</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>70549</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>206822</t>
+          <t>208896</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>122132</t>
+          <t>120764</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>163400</t>
+          <t>160119</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>174727</t>
+          <t>179452</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>349142</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>255736</t>
+          <t>264001</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>381948</t>
+          <t>383751</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>235356</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>328744</t>
+          <t>329673</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>530840</t>
+          <t>536943</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>691546</t>
+          <t>695730</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1578156</t>
+          <t>1579914</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2107175</t>
+          <t>2170613</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1297094</t>
+          <t>1311584</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1714346</t>
+          <t>1720948</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3060550</t>
+          <t>3022582</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3689488</t>
+          <t>3725865</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1077680</t>
+          <t>1060345</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1518127</t>
+          <t>1516187</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1645345</t>
+          <t>1638491</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2136723</t>
+          <t>2096734</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2892755</t>
+          <t>2869289</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3495261</t>
+          <t>3526907</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47888</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>124337</t>
+          <t>128436</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104536</t>
+          <t>110833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147731</t>
+          <t>146000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94232</t>
+          <t>107460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121739</t>
+          <t>136129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>232155</t>
+          <t>249691</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207734</t>
+          <t>226587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261250</t>
+          <t>272658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>177655</t>
+          <t>181530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155829</t>
+          <t>164682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>198838</t>
+          <t>199523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>165502</t>
+          <t>178479</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150694</t>
+          <t>164438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180260</t>
+          <t>192918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>343157</t>
+          <t>360009</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>314750</t>
+          <t>336448</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>367219</t>
+          <t>384038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>104058</t>
+          <t>105820</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>82711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>127215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95282</t>
+          <t>102508</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79990</t>
+          <t>87117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112763</t>
+          <t>122390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>199340</t>
+          <t>208328</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169574</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229548</t>
+          <t>240236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>263866</t>
+          <t>270106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233125</t>
+          <t>240047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>292134</t>
+          <t>299979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>274445</t>
+          <t>288902</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253630</t>
+          <t>267294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>295092</t>
+          <t>309578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>538311</t>
+          <t>559009</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>503063</t>
+          <t>520696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>578657</t>
+          <t>595221</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>150466</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125977</t>
+          <t>130847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179910</t>
+          <t>182272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>145242</t>
+          <t>155084</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128390</t>
+          <t>135934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163820</t>
+          <t>174200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>295708</t>
+          <t>309804</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260811</t>
+          <t>279480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329475</t>
+          <t>344163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>36082</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44160</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74730</t>
+          <t>76260</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>134982</t>
+          <t>136997</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116666</t>
+          <t>120491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151466</t>
+          <t>155496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>118487</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104976</t>
+          <t>108039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133554</t>
+          <t>137797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>253469</t>
+          <t>258495</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231251</t>
+          <t>234593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276838</t>
+          <t>280184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>154272</t>
+          <t>150957</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138275</t>
+          <t>133008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172632</t>
+          <t>168517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>198801</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181880</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211802</t>
+          <t>213482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>351092</t>
+          <t>349758</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>328436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376487</t>
+          <t>375611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>313507</t>
+          <t>313635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>313507</t>
+          <t>313635</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>313507</t>
+          <t>313635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>662634</t>
+          <t>670016</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>662634</t>
+          <t>670016</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>662634</t>
+          <t>670016</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,67 +2093,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>25383</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18059</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35680</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23723</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13539</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35223</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>66034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92322</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72584</t>
+          <t>87701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>134196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>169074</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108583</t>
+          <t>97128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280651</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>261396</t>
+          <t>223698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197688</t>
+          <t>197547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393860</t>
+          <t>253535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>196670</t>
+          <t>238217</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175079</t>
+          <t>213816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>216667</t>
+          <t>261736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>281845</t>
+          <t>281536</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175959</t>
+          <t>264203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>339613</t>
+          <t>299042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>478514</t>
+          <t>519752</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>358198</t>
+          <t>491662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>540495</t>
+          <t>547714</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>311116</t>
+          <t>371566</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>311116</t>
+          <t>371566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>311116</t>
+          <t>371566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474642</t>
+          <t>420788</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>474642</t>
+          <t>420788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474642</t>
+          <t>420788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>785757</t>
+          <t>792354</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>785757</t>
+          <t>792354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>785757</t>
+          <t>792354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54045</t>
+          <t>63635</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>53125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66159</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>65941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>118960</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88703</t>
+          <t>104424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117557</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>119449</t>
+          <t>136297</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107977</t>
+          <t>122551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130414</t>
+          <t>146888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>158352</t>
+          <t>169111</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147979</t>
+          <t>158927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166024</t>
+          <t>177516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>277801</t>
+          <t>305409</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262445</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290936</t>
+          <t>320190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>41706</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>67949</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>117752</t>
+          <t>117051</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103001</t>
+          <t>102706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133430</t>
+          <t>130926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>114944</t>
+          <t>117865</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102116</t>
+          <t>105138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128331</t>
+          <t>130858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>232696</t>
+          <t>234916</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213010</t>
+          <t>215566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251168</t>
+          <t>255375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121885</t>
+          <t>118932</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105783</t>
+          <t>105378</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>132127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>125839</t>
+          <t>127888</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111824</t>
+          <t>114817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138525</t>
+          <t>140845</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>246820</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227909</t>
+          <t>228020</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267907</t>
+          <t>267051</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>90388</t>
+          <t>99034</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>77294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121817</t>
+          <t>125208</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>54440</t>
+          <t>78412</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>63750</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>78975</t>
+          <t>96563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>144828</t>
+          <t>177446</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>185156</t>
+          <t>208323</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>210060</t>
+          <t>256629</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>181266</t>
+          <t>226801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>236563</t>
+          <t>288738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>222360</t>
+          <t>264705</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107020</t>
+          <t>239273</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301140</t>
+          <t>289318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>432420</t>
+          <t>521334</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>264998</t>
+          <t>481717</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>515674</t>
+          <t>559401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>322802</t>
+          <t>362941</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>291153</t>
+          <t>333152</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>352215</t>
+          <t>396534</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>571823</t>
+          <t>428249</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>476202</t>
+          <t>399431</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>715263</t>
+          <t>453444</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>894624</t>
+          <t>791191</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>789957</t>
+          <t>751838</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1114346</t>
+          <t>830694</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1471872</t>
+          <t>1489971</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1471872</t>
+          <t>1489971</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1471872</t>
+          <t>1489971</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>51246</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>68535</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>59023</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>62569</t>
+          <t>73704</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>93157</t>
+          <t>110268</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>92476</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118254</t>
+          <t>132441</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>739144</t>
+          <t>581753</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>659651</t>
+          <t>555053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>836288</t>
+          <t>609597</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,27 +4065,27 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>528097</t>
+          <t>614548</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>505953</t>
+          <t>591196</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>548994</t>
+          <t>635852</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1267241</t>
+          <t>1196301</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1187447</t>
+          <t>1156382</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1409849</t>
+          <t>1228424</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>145885</t>
+          <t>164373</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>139647</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>208896</t>
+          <t>188775</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>139572</t>
+          <t>157760</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>120764</t>
+          <t>139133</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>160119</t>
+          <t>180311</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>285456</t>
+          <t>322134</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>179452</t>
+          <t>290638</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>349142</t>
+          <t>356105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928123</t>
+          <t>797372</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928123</t>
+          <t>797372</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928123</t>
+          <t>797372</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1645854</t>
+          <t>1628703</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1645854</t>
+          <t>1628703</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1645854</t>
+          <t>1628703</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>328614</t>
+          <t>354638</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>264001</t>
+          <t>314782</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>383751</t>
+          <t>398559</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>292197</t>
+          <t>338119</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>235356</t>
+          <t>307751</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>329673</t>
+          <t>371825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>692756</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>536943</t>
+          <t>639373</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>695730</t>
+          <t>748690</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1736507</t>
+          <t>1664437</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1579914</t>
+          <t>1601546</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2170613</t>
+          <t>1729154</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1582867</t>
+          <t>1697968</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1311584</t>
+          <t>1647252</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1720948</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3319374</t>
+          <t>3362404</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3022582</t>
+          <t>3275951</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3725865</t>
+          <t>3450220</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1389084</t>
+          <t>1507968</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1440062</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1516187</t>
+          <t>1570302</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1784993</t>
+          <t>1696910</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1638491</t>
+          <t>1644444</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2096734</t>
+          <t>1748824</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3174077</t>
+          <t>3204877</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2869289</t>
+          <t>3112574</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3526907</t>
+          <t>3284075</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
